--- a/materials/Excel_in_class_exercises_solutions.xlsx
+++ b/materials/Excel_in_class_exercises_solutions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644829AB-3490-469F-9209-8C9FC628A19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA62A370-5AD3-452B-ADE3-F0E2C5A309E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Future_Value" sheetId="9" r:id="rId1"/>
@@ -22,10 +22,11 @@
     <sheet name="Installment" sheetId="13" r:id="rId7"/>
     <sheet name="Annuity" sheetId="6" r:id="rId8"/>
     <sheet name="Exam" sheetId="20" r:id="rId9"/>
-    <sheet name="Bar_Sales" sheetId="24" r:id="rId10"/>
-    <sheet name="Gift" sheetId="29" r:id="rId11"/>
-    <sheet name="Grading" sheetId="25" r:id="rId12"/>
-    <sheet name="Clients" sheetId="34" r:id="rId13"/>
+    <sheet name="Department" sheetId="35" r:id="rId10"/>
+    <sheet name="Bar_Sales" sheetId="24" r:id="rId11"/>
+    <sheet name="Gift" sheetId="29" r:id="rId12"/>
+    <sheet name="Grading" sheetId="25" r:id="rId13"/>
+    <sheet name="Clients" sheetId="34" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="solver_corr" hidden="1">1</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="167">
   <si>
     <t>DAX</t>
   </si>
@@ -490,6 +491,66 @@
   </si>
   <si>
     <t>"=AVERAGE(VLOOKUP($F$13,$A$2:$G$11,3,FALSE)+VLOOKUP($F$13,$A$2:$G$11,5,FALSE)+VLOOKUP($F$13,$A$2:$G$11,7,FALSE))/15*10"</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Hooloway</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Number of people in the Credit Department</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>Sum of salaries in the Credit Department</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t>Average salary in the Credit Department</t>
+  </si>
+  <si>
+    <t>Foster</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Number of people with salary&lt;200000</t>
+  </si>
+  <si>
+    <t>Watson</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Sum of these salaries</t>
+  </si>
+  <si>
+    <t>Dawkins</t>
+  </si>
+  <si>
+    <t>Average of these salaries</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Johnson</t>
   </si>
 </sst>
 </file>
@@ -768,7 +829,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -899,6 +960,7 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Currency 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5284,6 +5346,165 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD5998D-A737-4F40-91F0-00694D232188}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" customWidth="1"/>
+    <col min="5" max="5" width="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2">
+        <v>300000</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2">
+        <f>COUNTIF(B2:B9,"Credit")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3">
+        <v>270000</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3">
+        <f>SUMIF(B2:B9,"Credit",C2:C9)</f>
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4">
+        <v>180000</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4">
+        <f>AVERAGEIF(B2:B9,"Credit",C2:C9)</f>
+        <v>187500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5">
+        <v>235000</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5">
+        <f>COUNTIF(C2:C9,"&lt;200000")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6">
+        <v>150000</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6">
+        <f>SUMIF(C2:C9,"&lt;200000",C2:C9)</f>
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7">
+        <v>420000</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7">
+        <f>AVERAGEIF(C2:C9,"&lt;200000",C2:C9)</f>
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8">
+        <v>305000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9">
+        <v>195000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:H28"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -5673,7 +5894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B2:J25"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -6178,7 +6399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -6565,7 +6786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/materials/Excel_in_class_exercises_solutions.xlsx
+++ b/materials/Excel_in_class_exercises_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA62A370-5AD3-452B-ADE3-F0E2C5A309E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA95FE8-35E7-43C4-9AB6-B9F61DE7F43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Future_Value" sheetId="9" r:id="rId1"/>
@@ -46,11 +46,22 @@
     <definedName name="solver_ucut" hidden="1">1E+30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="166">
   <si>
     <t>DAX</t>
   </si>
@@ -487,12 +498,6 @@
     <t>"=VLOOKUP($F$13,$A$2:$G$11,6,FALSE)*0.3"</t>
   </si>
   <si>
-    <t>TODO: update the formula in F17 (should be identical to H17)</t>
-  </si>
-  <si>
-    <t>"=AVERAGE(VLOOKUP($F$13,$A$2:$G$11,3,FALSE)+VLOOKUP($F$13,$A$2:$G$11,5,FALSE)+VLOOKUP($F$13,$A$2:$G$11,7,FALSE))/15*10"</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
@@ -551,6 +556,9 @@
   </si>
   <si>
     <t>Johnson</t>
+  </si>
+  <si>
+    <t>"=AVERAGE(VLOOKUP($F$13,$A$2:$G$11,3,FALSE),VLOOKUP($F$13,$A$2:$G$11,5,FALSE),+VLOOKUP($F$13,$A$2:$G$11,7,FALSE))/15*10"</t>
   </si>
 </sst>
 </file>
@@ -558,8 +566,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -825,7 +833,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -909,12 +917,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -941,6 +949,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -960,7 +969,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Currency 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5297,10 +5305,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="58"/>
+      <c r="B1" s="59"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -5359,28 +5367,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="66" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="66" t="s">
-        <v>148</v>
+      <c r="B1" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2">
         <v>300000</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F2">
         <f>COUNTIF(B2:B9,"Credit")</f>
@@ -5389,16 +5397,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C3">
         <v>270000</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F3">
         <f>SUMIF(B2:B9,"Credit",C2:C9)</f>
@@ -5407,16 +5415,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4">
         <v>180000</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F4">
         <f>AVERAGEIF(B2:B9,"Credit",C2:C9)</f>
@@ -5425,16 +5433,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5">
         <v>235000</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F5">
         <f>COUNTIF(C2:C9,"&lt;200000")</f>
@@ -5443,16 +5451,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C6">
         <v>150000</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F6">
         <f>SUMIF(C2:C9,"&lt;200000",C2:C9)</f>
@@ -5461,16 +5469,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C7">
         <v>420000</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F7">
         <f>AVERAGEIF(C2:C9,"&lt;200000",C2:C9)</f>
@@ -5479,10 +5487,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>305000</v>
@@ -5490,10 +5498,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C9">
         <v>195000</v>
@@ -5518,10 +5526,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="63"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="17" t="s">
@@ -5574,12 +5582,12 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C10" s="17" t="s">
@@ -6312,10 +6320,10 @@
       <c r="H18" s="36"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="65"/>
+      <c r="C19" s="66"/>
       <c r="D19" s="36"/>
       <c r="E19" s="35" t="s">
         <v>98</v>
@@ -6755,12 +6763,12 @@
         <v>0.1</v>
       </c>
       <c r="F17" s="26">
-        <f>(_xlfn.XLOOKUP($F$13,$A$2:$A$11,$C$2:$C$11)+_xlfn.XLOOKUP($F$13,$A$2:$A$11,$E$2:$E$11)+_xlfn.XLOOKUP($F$13,$A$2:$A$11,$G$2:$G$11))/3*0.1</f>
-        <v>1.3666666666666667</v>
+        <f>AVERAGE(VLOOKUP($F$13,$A$2:$G$11,3,FALSE),VLOOKUP($F$13,$A$2:$G$11,5,FALSE),VLOOKUP($F$13,$A$2:$G$11,7,FALSE))/15*10</f>
+        <v>9.1111111111111107</v>
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="16" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6769,12 +6777,7 @@
       </c>
       <c r="F18" s="27">
         <f>SUM(F14:F17)</f>
-        <v>65.86666666666666</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F20" s="16" t="s">
-        <v>145</v>
+        <v>73.611111111111114</v>
       </c>
     </row>
     <row r="33" spans="11:11" x14ac:dyDescent="0.2">
@@ -6947,10 +6950,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="58"/>
+      <c r="B1" s="59"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -7469,12 +7472,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
@@ -10497,10 +10500,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="62"/>
+      <c r="B1" s="63"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
